--- a/output/rm2_sentiment/validation/human_master_v4/sentiment_v4_locked_test_adjudication.xlsx
+++ b/output/rm2_sentiment/validation/human_master_v4/sentiment_v4_locked_test_adjudication.xlsx
@@ -11,7 +11,7 @@
     <sheet name="LOCKED_TEST_ADJUDICATION" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LOCKED_TEST_ADJUDICATION'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'LOCKED_TEST_ADJUDICATION'!$A$1:$L$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -52,9 +52,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -448,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -527,8 +530,4605 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00125</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>7191322737258791707</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>7185096421220158747</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>azarine_retinol</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>azarine_retinol</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>pratista emang beneran bagus &amp; mencerahkan sih tapi mahal, aku kalo pas promo doang belinya. skrng mau nyoba the originote yg versi low budget nya</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Menilai Pratista bagus dan mencerahkan meski mahal.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Memuji efektivitas Pratista tetapi mengeluhkan harganya mahal.</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00181</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>7206961415776928539</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>7185096421220158747</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>azarine_retinol</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>azarine_retinol</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>@Marselli Septia lewat ra</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Hanya menandai akun lain.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Tag dan frasa singkat tidak cukup untuk menentukan orientasi sentimen.</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Hanya menandai akun lain dan mengarahkannya untuk lewat atau melihat, tanpa evaluasi sentimen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00183</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>7207084711930725146</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>7185096421220158747</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>azarine_retinol</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>azarine_retinol</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>iya lg😭</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Persetujuan singkat dengan emoji sedih tanpa konteks sebelumnya.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan persetujuan emosional tanpa konteks lengkap.</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Persetujuan singkat dengan emoji sedih tanpa objek atau pernyataan sebelumnya; orientasinya tidak dapat dipastikan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00242</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>7219702498860122907</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>7182401543491128602</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>caranya gmna SH ka KLO mau beli ak GK bisa</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Mengeluhkan kesulitan membeli produk.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Menanyakan cara membeli karena mengalami kesulitan.</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00315</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>7226746381418365723</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>7194330759329631514</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>originote_niacinamide</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>originote_niacinamide</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Bnerr bngtt</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Persetujuan sangat kuat.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan persetujuan kuat tanpa konteks lengkap.</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00346</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>7232501925241357082</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7185096421220158747</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>azarine_retinol</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>azarine_retinol</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>iya</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Jawaban 'iya' tanpa konteks pertanyaan sebelumnya.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Jawaban afirmatif tanpa konteks pertanyaan.</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Jawaban afirmatif 'iya' tidak memiliki pertanyaan atau objek sebelumnya, sehingga sentimennya tidak dapat ditentukan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00405</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>7258531980106121990</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>7242204399928593669</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>originote_niacinamide</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>originote_niacinamide</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>bisa kaa</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Jawaban sangat afirmatif.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Jawaban afirmatif tanpa pertanyaan yang tersedia.</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00500</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>7309508697428312837</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7306081689422351622</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>originote_niacinamide</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>originote_niacinamide</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>harusnya si bisa yah kaa, tp balik lagi ke kulit masing masing yaah kalo penasaran coba ajaa 🥰</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Meyakinkan kemungkinan bisa dan mendorong untuk mencoba.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan kemungkinan bisa tetapi hasil kembali pada kondisi kulit masing-masing.</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00631</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>7320602655682937606</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7312025661835578629</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Wajib pake moist dong, bisa bgt</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Jawaban afirmatif dan menekankan wajib memakai pelembap.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Menegaskan pelembap wajib dan dapat digunakan.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00692</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>7330585451604329222</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>7237379067773766917</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>azarine_retinol</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>azarine_retinol</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Iya lg aktif kl sakit</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Pernyataan singkat tidak cukup jelas tanpa konteks.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Kalimat tidak lengkap mengenai kondisi aktif dan sakit.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Kalimat mengenai kondisi aktif dan sakit tidak lengkap dan tidak dapat ditafsirkan secara memadai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00779</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>7342821932075729670</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>7340938843190725893</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Bener bgt kak aku juga gitu</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Persetujuan dan pengalaman serupa.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan pengalaman yang sama tanpa konteks lengkap.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00856</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>7357863055097299718</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>7357662447248968966</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Kinclong bgt bund😌, cuma sanggup beli sekali abis itu boncos</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Memuji hasil sangat kinclong meski hanya mampu membeli sekali.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Memuji hasil sangat kinclong tetapi mengeluhkan hanya mampu membeli sekali.</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00879</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>7357955987939148550</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>7357662447248968966</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Kak skincaremu bikin dompetku meraung raungg 😭 tapi cakep parah</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Mengeluhkan dompet tetapi menilai hasil sangat bagus.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Memuji skincare sangat bagus tetapi mengeluhkan dompet terbebani.</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00912</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>7358240058845315845</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>7357662447248968966</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>malah takut cocok, yg ga cocok kantong ku 😌</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Khawatir cocok di wajah tetapi tidak terjangkau dompet.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Mengkhawatirkan produk cocok karena kantong tidak mampu menanggung harganya.</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Mengungkapkan kekhawatiran produk mungkin cocok tetapi harganya tidak terjangkau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00934</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>7358710079295750917</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>7357662447248968966</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>bener 😭</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Persetujuan singkat dengan emoji sedih, konteks terbatas.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan persetujuan tanpa konteks lengkap.</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>V4MA00968</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>7359784259962766085</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>7357662447248968966</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>save dulu , kalo dah kaya balik lagi🤗🔥</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Menyimpan informasi untuk membeli saat sudah mampu.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Menyimpan informasi untuk kembali membeli ketika sudah mampu.</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01116</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>7378467869967500037</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>7378347819268082950</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>cuma bisa nelen ludah Adah dah ah pengen tapi duit nya ga kebagian terus 😭</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Sangat ingin membeli tetapi uang tidak tersedia.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan ingin membeli tetapi tidak memiliki cukup uang.</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01217</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>7389278695179551493</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>7389110955214490886</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>di tempatku harganya lebih murah, tpi takut bukan yg asli kak</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Khawatir harga murah menandakan produk tidak asli.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Menemukan harga lebih murah tetapi khawatir produk tidak asli.</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01274</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>7398117043981484806</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>7397028146429709573</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>azarine_retinol</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>azarine_retinol</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Samarin bisaa hihi tp gaa bisa ilang total ya kalo pake skincare 🙈😍</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Menjelaskan produk dapat menyamarkan meski tidak menghilangkan total.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Menjelaskan bekas dapat disamarkan tetapi tidak hilang total dengan skincare.</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01305</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>7401131808035865349</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>7378347819268082950</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>😭😭😭😭 maap gatau kak soalany🙂</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Permintaan maaf dan tidak tahu jawabannya tanpa konteks pertanyaan.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Meminta maaf karena tidak mengetahui jawaban.</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Meminta maaf karena tidak mengetahui jawaban, tanpa evaluasi positif atau negatif.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01324</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>7404818621124674310</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>7385065641595653382</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>emang</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Kata 'emang' tanpa konteks pernyataan sebelumnya.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Jawaban persetujuan singkat tanpa konteks.</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Kata 'emang' merupakan respons bergantung konteks dan tidak cukup untuk menentukan orientasi sentimen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01325</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>7404848332438553349</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>7389110955214490886</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>kakak aku orang Palembang ❤️</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan berasal dari Palembang disertai emoji hati.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan berasal dari Palembang.</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01347</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>7408832152353145605</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>7378347819268082950</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>pngn bgt nyobain</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Menunjukkan keinginan kuat untuk mencoba.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan sangat ingin mencoba.</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01395</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>7420293851044184838</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>7418812570569641221</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Jangan😭😭</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Larangan singkat dengan emoji sedih tanpa objek yang jelas.</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Memberikan larangan tanpa konteks pertanyaan.</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Larangan singkat dengan emoji sedih tidak menyebut objeknya, sehingga orientasi sentimen tidak dapat dipastikan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01407</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>7421158445472301830</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>ini c promo c produc baru lagi</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Spekulasi bahwa konten merupakan promosi produk baru.</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Sindiran bahwa kontroversi dijadikan promosi produk baru.</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01409</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>7421174441659794182</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>udah kaya kak gpp 😂 haahha</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Respons bercanda bahwa harga tidak masalah karena kreator kaya.</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Candaan 'sudah kaya' dapat berupa dukungan atau sindiran.</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01440</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>7421213355824874245</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>ang ang ang🤣🤣🤣</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Tawa meniru ungkapan tertentu dan membutuhkan konteks video.</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Menirukan ejekan atau ucapan sebelumnya dengan nada tertawa.</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Tiruan bunyi disertai tawa dapat berupa candaan atau ejekan; tanpa konteks, orientasinya tidak dapat ditentukan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01460</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>7421252247012852485</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>udah cek lab dan hasil nya sama dengan hasil di kemasan.. 😂😂😂</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Pernyataan hasil lab sesuai kemasan disertai tawa yang tampak sarkastik.</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Pernyataan hasil lab sesuai kemasan disertai tawa dapat literal atau sarkastik.</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Hasil pemeriksaan laboratorium dinyatakan sama dengan informasi pada kemasan, sehingga komentar mengonfirmasi klaim produk dan berorientasi positif. Emoji tertawa tidak cukup untuk menetapkan sarkasme tanpa konteks tambahan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01464</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>7421280895884313350</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Untung ketahuan</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Merasa beruntung masalah akhirnya terbongkar.</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan beruntung masalah diketahui.</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01473</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>7421307121150968581</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>😁😁😁😁😁😁 akhirnya . @dokterdetektif gimana nih dok?</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Ungkapan lega 'akhirnya' disertai emoji ceria, tetapi konteks terbatas.</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Ekspresi 'akhirnya' dan emoji tidak menjelaskan apakah respons positif atau mengejek.</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01476</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>7421310440956134149</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Nahkan.. Sering nemuin komen kya gini makanya jd takut😭</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Sering melihat keluhan serupa sehingga takut.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Mengaku takut setelah sering melihat komentar negatif.</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01509</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>7421339217391010566</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>setiap wajah tidak sama kak mungkin di aq kurang cocok aj</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Menjelaskan kemungkinan ketidakcocokan personal.</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan produk kurang cocok pada dirinya.</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01560</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>7421415498577412870</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Alhamdulilah bangdt dlo sempet mau pzke devin tapi hati ini ragu</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Bersyukur tidak jadi memakai Daviena karena sempat ragu.</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>Bersyukur tidak jadi memakai Daviena setelah sebelumnya ragu.</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01645</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>7421753520572859142</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>syg bgt ngapain dibuang , orang cuma overclaim aja , harusnya abisin aja 😌 soalnya mahalll</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Menyarankan menghabiskan produk karena mahal meski hanya overclaim.</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>Mengakui overclaim dan harga mahal meski menyarankan produk dihabiskan.</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01664</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>7421800568148837125</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Hampir ke goda 😂</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Merasa beruntung hampir tergoda tetapi tidak jadi membeli.</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan hampir tergoda membeli tetapi tidak memberi evaluasi pengalaman.</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01691</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>7421914328532927237</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>dimurahin aja biar anak sekolah juga bisa kebeli</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Meminta harga diturunkan agar pelajar mampu membeli.</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Menyarankan harga diturunkan agar pelajar mampu membeli.</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01704</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>7422095352289362694</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>aku GK pernah sentuh🤣</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan tidak pernah menyentuh produk.</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan tidak pernah memakai atau menyentuh produknya.</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01751</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>7422283530959307525</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>pindah usaha yg lain kyknya ka mulai beelajar dri pengalaman</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Saran berpindah usaha dan belajar dari pengalaman.</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>Menyarankan berpindah usaha dan belajar dari pengalaman.</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01769</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>7422428877157696261</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>soalnya udah terbukti😅</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Pernyataan 'sudah terbukti' mengacu bukti negatif dalam konteks sebelumnya.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan sesuatu sudah terbukti tetapi objeknya tidak disebutkan.</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01814</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>7422638069448852229</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>jangankan pakai liat aja blm prnh 🤭</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan bahkan belum pernah melihat atau memakai produk.</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan belum pernah memakai maupun melihat produk.</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01834</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>7422699211601625862</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>alhamdulillah saya tidak pakai daviena🙏</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Bersyukur tidak memakai Daviena.</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Bersyukur tidak menggunakan Daviena.</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01847</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>7422810968974197510</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>udh coba Gonta ganti yg viral berharap cocok malah jerawatan parah,alhasil di sembuhin pake Pond's udh pake 1minggu Alhamdulillah jerawat berkurang</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Setelah gagal dengan produk viral, Pond's mengurangi jerawat dalam seminggu.</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>Mengeluhkan produk viral menyebabkan jerawat parah, lalu membaik dengan Pond's.</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01853</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>7422831633167844101</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>akhiirnyaaahhh.....</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Ungkapan lega 'akhirnya' tanpa objek lengkap.</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Ungkapan 'akhirnya' tanpa objek dapat berupa lega atau sindiran.</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01859</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>7422854456663180040</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>7389110955214490886</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2% ditambah 3% jadilah 25% 😅</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Mengejek perhitungan persentase yang tidak masuk akal.</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Candaan perhitungan persentase tanpa evaluasi produk yang jelas.</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01903</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>7424291244614370053</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>7421364555957275910</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>assalamualaikum salam silaturahmi saudara ku di Jumat Mubarak 🤲🙏🥰🤗@teteh endang anu geuliss @Ayyuan3</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Salam silaturahmi dan doa Jumat Mubarak.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Berisi salam dan sapaan silaturahmi tanpa evaluasi produk.</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01913</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>7424385701883970322</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>7424146834534239493</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>KK maaf mau tanya saya beli maryame kemaren kok ada tulisan maryame di bawah botolnya
+tpi yg sudah" ngk ada tulisan itu di bawah botol cream siang nya itu ORI atao kW atao gmna tolong ksh tau</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Khawatir perbedaan tulisan pada botol menandakan produk palsu.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Menanyakan keaslian produk berdasarkan perbedaan tulisan pada bagian bawah botol.</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01956</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>7426334720056034053</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>7421364555957275910</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>isinya di banyakin dong owner maryame</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Meminta isi produk diperbanyak, mengisyaratkan isi terlalu sedikit.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Meminta pemilik menambah jumlah isi tanpa evaluasi kualitas yang jelas.</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01971</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>7428111116586861318</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>7418514646698642693</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>kak.aku kemarin co di shopee yg maryame official store dpt harga 47,,ORI apa bukan ya😭</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Khawatir harga sangat murah menandakan produk tidak asli.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Menanyakan keaslian produk karena harga yang didapat sangat murah.</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>V4MA01976</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>7428438943307760385</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>7428436533981613318</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>krim sam sam dok di daerah ku bnyak bnngt yg make pdhl mencurigakan.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Meminta pemeriksaan krim Sam Sam yang dianggap mencurigakan.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan produk mencurigakan meski banyak digunakan di daerahnya.</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02016</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>7428461574057034504</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>7428436533981613318</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>otw maryame</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan akan beralih atau membeli Maryame.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan niat menuju atau mencoba Maryame tanpa evaluasi.</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02049</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>7428506119012664070</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>7428436533981613318</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>kasihkan ke aku dong daripada enggak digunain wkw</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Permintaan bercanda agar produk diberikan daripada tidak dipakai.</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Meminta produk yang tidak digunakan tanpa memberi evaluasi kualitas.</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02104</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>7428591121852498694</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>7428436533981613318</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>gladglow dok🥰</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Menyebut Gladglow disertai emoji kasih sayang.</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Menyebut Gladglow sebagai usulan pembahasan; emoji tidak cukup menunjukkan evaluasi produk.</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02111</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>7428598322796135186</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>7428436533981613318</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>dokter plisss kymm skin 🙏🏻
+terutama SS nya
+masih 3 botol ini tapi was² polll</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Masih memiliki tiga botol sunscreen tetapi sangat khawatir menggunakannya.</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>Meminta pemeriksaan KYMM Skin karena merasa waswas sebelum menggunakan stok yang dimiliki.</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02126</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>7428619039407309573</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>7428436533981613318</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>dok , creamnya buat aku aja 😂🥰</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>Permintaan bercanda agar krim diberikan kepadanya.</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>Secara bercanda meminta krim untuk dirinya tanpa evaluasi eksplisit.</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02169</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>7428803531065377537</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>7428436533981613318</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>@Dilahh tuh dil di cek aman cenah.. tapi mahal wkwk</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>Menyampaikan hasil pemeriksaan aman tetapi harganya mahal.</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Menyebut produk aman tetapi sekaligus mengeluhkan harganya mahal; orientasinya campuran.</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Menyampaikan informasi bahwa produk dikatakan aman sekaligus mahal; orientasi campuran dan berbentuk laporan, bukan evaluasi final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02292</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>7429647546739720965</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>7401739344085585158</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Mai co tapi gak ada</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>Ingin checkout tetapi produk tidak tersedia.</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan ingin checkout tetapi barang tidak ada; objek dan evaluasinya kurang jelas.</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02312</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>7430023892197442309</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>7428436533981613318</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>ff owner no 1 makassar dong. jgn dilangkahin jgn ada udang dibalik batu 😆</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>Mencurigai brand FF dilewati dan ada kepentingan tersembunyi.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Meminta produk FF tidak dilewatkan dalam pemeriksaan sambil menyiratkan kecurigaan terhadap alasan pengabaian.</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, konflik antara Neutral dan Negative diselesaikan sebagai Neutral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02321</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>7430172210877350663</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>7430007251076697350</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>sabar say,nama'y skincare aman bpom ya ga instan ,klo yg semingu putih glowing itu yg ber mercurut,hd 😂😂</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>Saran sabar karena skincare aman tidak memberi hasil instan.</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>Membela skincare aman ber-BPOM dan menjelaskan bahwa hasilnya tidak instan.</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02366</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>7431010926126547728</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>7429636271552728326</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Pasar terbuka skincare laris semua berwajah berwajah putih</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>Pernyataan tidak jelas dan tidak menunjukkan evaluasi spesifik.</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Pernyataan umum tentang pasar skincare dan wajah putih tidak memberi evaluasi produk yang jelas.</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Pernyataan umum tentang pasar skincare dan wajah putih tidak memuat evaluasi produk yang cukup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02441</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>7435488247784670008</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>7428436533981613318</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Wih expedisinya ID express dongg</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>Menunjukkan ketertarikan pada ekspedisi ID Express.</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>Hanya mengamati bahwa jasa pengiriman yang digunakan adalah ID Express.</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02452</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>7436930583521592071</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>7421364555957275910</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>enggak kak aku udah habis 2pot</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>Jawaban 'tidak' dan sudah habis dua pot tanpa konteks pertanyaan.</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Hanya menyatakan sudah menghabiskan dua pot tanpa evaluasi hasil.</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan telah menghabiskan dua pot tanpa menjelaskan hasil atau evaluasi pemakaian.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02484</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>7439013651774014215</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>7357662447248968966</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>😂😂😂</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>Emoji tertawa tanpa teks tidak menunjukkan objek sentimen.</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>Emoji tertawa menunjukkan respons positif atau terhibur, tetapi objeknya implisit.</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02571</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>7450895883666129671</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>😫</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>Emoji tertekan tanpa teks tidak memberi konteks sentimen.</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Emoji tertekan menunjukkan emosi negatif, tetapi penyebab dan objeknya tidak tertulis.</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Emoji tertekan menunjukkan emosi negatif yang jelas terhadap konteks komentar atau video.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02608</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>7457073971276825351</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>7279666593129434374</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>nggako</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>Jawaban singkat 'nggak kok' tanpa konteks pertanyaan.</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>Jawaban singkat 'nggak kok' tidak memuat objek atau evaluasi yang cukup tanpa konteks.</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Jawaban 'nggak kok' tidak memiliki objek atau pertanyaan sebelumnya, sehingga makna sentimennya tidak dapat ditentukan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02760</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>7479628348084962054</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>7421104723333483782</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>😂</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>Emoji tertawa tanpa teks tidak cukup menentukan sentimen.</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Emoji tertawa menunjukkan respons terhibur, tetapi objeknya implisit.</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02796</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>7496089727645319952</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>7357662447248968966</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>daviena_retinol</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>iyah bagus. tapi dompetku kurang setuju</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>Menilai produk bagus meski harganya tidak ramah dompet.</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>Mengakui produk bagus tetapi sekaligus mengeluhkan harganya tidak sesuai kemampuan.</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02833</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>7510056071991313160</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>7472351771025755410</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>iya mba sama lagi nabungg😭</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>Mengeluhkan harus menabung untuk membeli.</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan mengalami hal yang sama dan sedang menabung, tetapi objek serta keluhannya bergantung pada konteks.</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Menyatakan sedang menabung disertai emoji menangis, yang menunjukkan keluhan keterjangkauan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>V4MA02859</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>7524369884999303943</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>7279666593129434374</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>😅 cc @maryame.official</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>Emoji senyum dan tag merek tanpa pernyataan evaluatif.</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>Emoji tersenyum disertai tag merek menunjukkan respons positif, tetapi evaluasinya tidak eksplisit.</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>V4MA03021</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>7589230361332171527</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>7507827983269350661</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>😁 cc @maryame.official</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>Emoji senyum dan tag merek tanpa teks evaluatif.</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Emoji senyum disertai tag merek menunjukkan respons positif, tetapi evaluasinya implisit.</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>V4MA03075</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>7596296494510375700</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>7596239649517899016</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>night cream ultimate Sm insentive night cream with aha beda produk apa sma?
+soalnya d aku ccok yg ultimate</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>Pertanyaan apakah dua jenis night cream merupakan produk berbeda.</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>Menanyakan perbedaan dua produk sambil menyatakan dirinya cocok memakai varian Ultimate.</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>V4MA03088</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>7596529379095495445</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>7596239649517899016</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>bnyk bgt yg belain 😹😹</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Mengejek banyaknya orang yang membela dalam konteks kontroversi.</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Pernyataan tentang banyaknya orang yang membela dapat berupa observasi atau sindiran; orientasinya tidak jelas.</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Pernyataan tentang banyaknya orang yang membela disertai emoji mengejek menunjukkan sindiran negatif dalam konteks kontroversi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>V4MA03130</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>7610285190547981076</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>7279666593129434374</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>maryame_niacinamide</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>😂</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>Emoji tertawa tanpa teks tidak cukup menentukan sentimen.</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Emoji tertawa menunjukkan respons terhibur, tetapi objeknya implisit.</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>V4MA03143</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>7624915654769246983</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>7596239649517899016</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>davina_skincare</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>😂😂😂</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Uncertain</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>Emoji tertawa tanpa teks tidak cukup menentukan sentimen.</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Emoji tertawa menunjukkan respons terhibur, tetapi objeknya tidak tertulis.</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>V4MA03156</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>7644004522876044053</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>7327630114282573061</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>azarine_retinol</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>azarine_retinol</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Bisa banget kak</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>Jawaban sangat afirmatif.</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>Memberi jawaban afirmatif bahwa sesuatu dapat dilakukan tanpa evaluasi produk.</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Sesuai aturan adjudikasi, karena salah satu annotator memberi label Positive, label akhir ditetapkan Positive.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:L75"/>
+  <dataValidations count="1">
+    <dataValidation sqref="K2:K75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Negative,Neutral,Positive,Uncertain,No Text"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>